--- a/reference/governance/sdlc/assets/evolith-sdlc-implementation-workbook.xlsx
+++ b/reference/governance/sdlc/assets/evolith-sdlc-implementation-workbook.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuración Base" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz RACI SDLC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard Adopción" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-Equipo y Contexto" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-Matriz RACI" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-Quality Gates (Ejemplos)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-Matriz Riesgos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +45,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E3A5F"/>
         <bgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F4F6"/>
+        <bgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,10 +78,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,67 +454,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Equipo / Producto</t>
+          <t>Sección</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sponsor</t>
+          <t>Instrucciones de Uso</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Arquitecto / Tech Lead</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha Inicio</t>
+          <t>Responsable de Llenado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>[Nombre Producto]</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[Sponsor]</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[PO]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>[TL]</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Contexto y Equipo</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Registrar el nombre oficial del sistema, sponsor ejecutivo, roles clave de producto y tecnología.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Scrum Master / Agile Coach</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Matriz RACI SDLC</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Asignar NOMBRES PROPIOS a cada una de las responsabilidades a lo largo del ciclo de vida SDLC.</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tech Lead / Arquitecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Quality Gates</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Personalizar los umbrales de cobertura y seguridad exigidos antes de permitir pases a los ambientes.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SecOps / QA Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Riesgos</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Registrar riesgos arquitectónicos o dependencias bloqueantes que puedan impedir el delivery.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Product Owner / Tech Lead</t>
         </is>
       </c>
     </row>
@@ -509,174 +558,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fase</t>
+          <t>Rol SDLC</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Artefacto Requerido</t>
+          <t>Nombre / Área</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Responsible (R)</t>
+          <t>Email de Contacto</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Accountable (A)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Consulted (C)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Informed (I)</t>
+          <t>Nivel de Decisión</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1. Concepción</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Product Requirements Document (PRD)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sponsor Ejecutivo</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ej: Director de Área</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>sponsor@empresa.com</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobación Presupuestal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Product Owner</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Sponsor</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Arquitecto</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Equipo Dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2. Diseño</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Registro de Decisión (ADR)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Arquitecto</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Arquitecto</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Ej: PO Core Bancario</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>po@empresa.com</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Aprobación de Requerimientos (PRD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Arquitecto Asignado</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Ej: Arquitecto de Soluciones</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>arq@empresa.com</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobación de Diseño Técnico (ADR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Tech Lead</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Equipo Dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2. Diseño</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Historias Funcionales</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>UX / Tech Lead</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4. Validación</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Test Summary Report</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Ej: Líder Técnico</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>tl@empresa.com</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Validación de PRs y Pase a QA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>QA Lead</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Tech Lead</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sponsor</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ej: Líder Calidad</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>qa@empresa.com</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobación de Pase a Producción</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>DevOps / SecOps</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Ej: Especialista Seguridad</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>sec@empresa.com</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Revisión de Vulnerabilidades (DAST/SAST)</t>
         </is>
       </c>
     </row>
@@ -691,69 +732,680 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="57" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Métrica Macro</t>
+          <t>Fase SDLC</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Criterio de Éxito</t>
+          <t>Artefacto Requerido</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Estado (Pass/Fail)</t>
+          <t>Responsible (R)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Accountable (A)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Consulted (C)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Informed (I)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cobertura Estática</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Todos los proyectos en SonarQube con &gt; 80%</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1. Concepción</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Product Requirements Document (PRD)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>UX / Arquitecto</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Equipo Dev</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Gobernanza Arquitectónica</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>100% de cambios estructurales con un ADR documentado</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1. Concepción</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Aprobación del Presupuesto</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Finanzas</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Arquitecto</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Trazabilidad SDLC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Todo Commit enlaza a un Ticket / Issue</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2. Diseño</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Registro de Decisión (ADRs Principales)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Arquitecto</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Arquitecto</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>SecOps / Infra</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Equipo Dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2. Diseño</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Diagramas de Secuencia y Entidad-Relación</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Arquitecto</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2. Diseño</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Criterios de Aceptación Funcional</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>QA Lead</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>3. Construcción</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Código y Unit Tests (Pull Requests)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Especialista Security</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>3. Construcción</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Especificación de APIs (Swagger/OpenAPI)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Desarrollador</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Arquitecto</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Frontend / Consumidores</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>4. Validación</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Plan de Pruebas de Estrés</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>QA Lead</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>4. Validación</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Reporte de Vulnerabilidades</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>SecOps</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>SecOps</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Arquitecto</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>5. Entrega</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Release Notes y Manual de Soporte</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>L2 Support</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ambiente Destino</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Métrica / Check</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Umbral Mínimo Requerido</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Aprobador</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Obligatoriedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Cobertura de Unit Tests (SonarQube)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>&gt; 80% líneas cubiertas</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Automatizado (CI)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Mandatorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Análisis SAST (Checkmarx/Veracode)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>0 Críticas, 0 Altas</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>SecOps</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Mandatorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Deuda Técnica SonarQube</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Calificación 'A'</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Condicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Porcentaje de Casos de Uso Exitosos</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>100% Casos Críticos, &gt;95% Alternativos</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>QA Lead</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Mandatorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PRODUCCIÓN</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Pruebas de Estrés y Rendimiento</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Latencia p99 &lt; 200ms</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Arquitecto</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Condicional (Según Tier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCCIÓN</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Infraestructura como Código (IaC)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Plantillas Terraform revisadas</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Mandatorio</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Descripción del Riesgo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Probabilidad (Alta/Med/Baja)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Impacto</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Estrategia de Mitigación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Capacidad</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>El equipo no conoce el framework de UI de Evolith</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Retraso de sprint 1 y 2</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Asignar un champion para pair programming</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Integración</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Las APIs Legacy no tienen documentación</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Fallos en UAT</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Agendar taller de descubrimiento funcional en Fase 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
